--- a/scripts/sample_ BFI-2.xlsx
+++ b/scripts/sample_ BFI-2.xlsx
@@ -461,7 +461,7 @@
         <v>性格外向，喜欢交际</v>
       </c>
       <c r="J2" t="str">
-        <v>我是一个……的人 1. 性格外向，喜欢交际</v>
+        <v>我是一个性格外向，喜欢交际的人</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +493,7 @@
         <v>心肠柔软，有同情心</v>
       </c>
       <c r="J3" t="str">
-        <v>我是一个……的人 2. 心肠柔软，有同情心</v>
+        <v>我是一个心肠柔软，有同情心的人</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         <v>缺乏条理</v>
       </c>
       <c r="J4" t="str">
-        <v>我是一个……的人 3. 缺乏条理</v>
+        <v>我是一个缺乏条理的人</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         <v>从容，善于处理压力</v>
       </c>
       <c r="J5" t="str">
-        <v>我是一个……的人 4. 从容，善于处理压力</v>
+        <v>我是一个从容，善于处理压力的人</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
         <v>对艺术没有什么兴趣</v>
       </c>
       <c r="J6" t="str">
-        <v>我是一个……的人 5. 对艺术没有什么兴趣</v>
+        <v>我是一个对艺术没有什么兴趣的人</v>
       </c>
     </row>
     <row r="7">
@@ -621,7 +621,7 @@
         <v>性格坚定自信，敢于表达自己的观点</v>
       </c>
       <c r="J7" t="str">
-        <v>我是一个……的人 6. 性格坚定自信，敢于表达自己的观点</v>
+        <v>我是一个性格坚定自信，敢于表达自己的观点的人</v>
       </c>
     </row>
     <row r="8">
@@ -653,7 +653,7 @@
         <v>为人恭谦，尊重他人</v>
       </c>
       <c r="J8" t="str">
-        <v>我是一个……的人 7. 为人恭谦，尊重他人</v>
+        <v>我是一个为人恭谦，尊重他人的人</v>
       </c>
     </row>
     <row r="9">
@@ -685,7 +685,7 @@
         <v>比较懒</v>
       </c>
       <c r="J9" t="str">
-        <v>我是一个……的人 8. 比较懒</v>
+        <v>我是一个比较懒的人</v>
       </c>
     </row>
     <row r="10">
@@ -717,7 +717,7 @@
         <v>经历挫折后仍能保持积极心态</v>
       </c>
       <c r="J10" t="str">
-        <v>我是一个……的人 9. 经历挫折后仍能保持积极心态</v>
+        <v>我是一个经历挫折后仍能保持积极心态的人</v>
       </c>
     </row>
     <row r="11">
@@ -749,7 +749,7 @@
         <v>对许多不同的事物都感兴趣</v>
       </c>
       <c r="J11" t="str">
-        <v>我是一个……的人 10. 对许多不同的事物都感兴趣</v>
+        <v>我是一个对许多不同的事物都感兴趣的人</v>
       </c>
     </row>
     <row r="12">
@@ -781,7 +781,7 @@
         <v>很少觉得兴奋或者特别想要(做)什么</v>
       </c>
       <c r="J12" t="str">
-        <v>我是一个……的人 11. 很少觉得兴奋或者特别想要(做)什么</v>
+        <v>我是一个很少觉得兴奋或者特别想要(做)什么的人</v>
       </c>
     </row>
     <row r="13">
@@ -813,7 +813,7 @@
         <v>常常挑别人的毛病</v>
       </c>
       <c r="J13" t="str">
-        <v>我是一个……的人 12. 常常挑别人的毛病</v>
+        <v>我是一个常常挑别人的毛病的人</v>
       </c>
     </row>
     <row r="14">
@@ -845,7 +845,7 @@
         <v>可信赖的，可靠的</v>
       </c>
       <c r="J14" t="str">
-        <v>我是一个……的人 13. 可信赖的，可靠的</v>
+        <v>我是一个可信赖的，可靠的的人</v>
       </c>
     </row>
     <row r="15">
@@ -877,7 +877,7 @@
         <v>喜怒无常，情绪起伏较多</v>
       </c>
       <c r="J15" t="str">
-        <v>我是一个……的人 14. 喜怒无常，情绪起伏较多</v>
+        <v>我是一个喜怒无常，情绪起伏较多的人</v>
       </c>
     </row>
     <row r="16">
@@ -909,7 +909,7 @@
         <v>善于创造，能找到聪明的方法来做事</v>
       </c>
       <c r="J16" t="str">
-        <v>我是一个……的人 15. 善于创造，能找到聪明的方法来做事</v>
+        <v>我是一个善于创造，能找到聪明的方法来做事的人</v>
       </c>
     </row>
     <row r="17">
@@ -941,7 +941,7 @@
         <v>比较安静</v>
       </c>
       <c r="J17" t="str">
-        <v>我是一个……的人 16. 比较安静</v>
+        <v>我是一个比较安静的人</v>
       </c>
     </row>
     <row r="18">
@@ -973,7 +973,7 @@
         <v>对他人没有什么同情心</v>
       </c>
       <c r="J18" t="str">
-        <v>我是一个……的人 17. 对他人没有什么同情心</v>
+        <v>我是一个对他人没有什么同情心的人</v>
       </c>
     </row>
     <row r="19">
@@ -1005,7 +1005,7 @@
         <v>做事有计划有条理</v>
       </c>
       <c r="J19" t="str">
-        <v>我是一个……的人 18. 做事有计划有条理</v>
+        <v>我是一个做事有计划有条理的人</v>
       </c>
     </row>
     <row r="20">
@@ -1037,7 +1037,7 @@
         <v>容易紧张</v>
       </c>
       <c r="J20" t="str">
-        <v>我是一个……的人 19. 容易紧张</v>
+        <v>我是一个容易紧张的人</v>
       </c>
     </row>
     <row r="21">
@@ -1069,7 +1069,7 @@
         <v>着迷于艺术、音乐或文学</v>
       </c>
       <c r="J21" t="str">
-        <v>我是一个……的人 20. 着迷于艺术、音乐或文学</v>
+        <v>我是一个着迷于艺术、音乐或文学的人</v>
       </c>
     </row>
     <row r="22">
@@ -1101,7 +1101,7 @@
         <v>常常处于主导地位，像个领导一样</v>
       </c>
       <c r="J22" t="str">
-        <v>我是一个……的人 21. 常常处于主导地位，像个领导一样</v>
+        <v>我是一个常常处于主导地位，像个领导一样的人</v>
       </c>
     </row>
     <row r="23">
@@ -1133,7 +1133,7 @@
         <v>常与他人意见不和</v>
       </c>
       <c r="J23" t="str">
-        <v>我是一个……的人 22. 常与他人意见不和</v>
+        <v>我是一个常与他人意见不和的人</v>
       </c>
     </row>
     <row r="24">
@@ -1165,7 +1165,7 @@
         <v>很难开始行动起来去完成一项任务</v>
       </c>
       <c r="J24" t="str">
-        <v>我是一个……的人 23. 很难开始行动起来去完成一项任务</v>
+        <v>我是一个很难开始行动起来去完成一项任务的人</v>
       </c>
     </row>
     <row r="25">
@@ -1197,7 +1197,7 @@
         <v>觉得有安全感，对自己满意</v>
       </c>
       <c r="J25" t="str">
-        <v>我是一个……的人 24. 觉得有安全感，对自己满意</v>
+        <v>我是一个觉得有安全感，对自己满意的人</v>
       </c>
     </row>
     <row r="26">
@@ -1229,7 +1229,7 @@
         <v>不喜欢知识性或者哲学性强的讨论</v>
       </c>
       <c r="J26" t="str">
-        <v>我是一个……的人 25. 不喜欢知识性或者哲学性强的讨论</v>
+        <v>我是一个不喜欢知识性或者哲学性强的讨论的人</v>
       </c>
     </row>
     <row r="27">
@@ -1261,7 +1261,7 @@
         <v>不如别人有活力</v>
       </c>
       <c r="J27" t="str">
-        <v>我是一个……的人 26. 不如别人有活力</v>
+        <v>我是一个不如别人有活力的人</v>
       </c>
     </row>
     <row r="28">
@@ -1293,7 +1293,7 @@
         <v>宽宏大量</v>
       </c>
       <c r="J28" t="str">
-        <v>我是一个……的人 27. 宽宏大量</v>
+        <v>我是一个宽宏大量的人</v>
       </c>
     </row>
     <row r="29">
@@ -1325,7 +1325,7 @@
         <v>有时比较没有责任心</v>
       </c>
       <c r="J29" t="str">
-        <v>我是一个……的人 28. 有时比较没有责任心</v>
+        <v>我是一个有时比较没有责任心的人</v>
       </c>
     </row>
     <row r="30">
@@ -1357,7 +1357,7 @@
         <v>情绪稳定，不易生气</v>
       </c>
       <c r="J30" t="str">
-        <v>我是一个……的人 29. 情绪稳定，不易生气</v>
+        <v>我是一个情绪稳定，不易生气的人</v>
       </c>
     </row>
     <row r="31">
@@ -1389,7 +1389,7 @@
         <v>几乎没有什么创造性</v>
       </c>
       <c r="J31" t="str">
-        <v>我是一个……的人 30. 几乎没有什么创造性</v>
+        <v>我是一个几乎没有什么创造性的人</v>
       </c>
     </row>
     <row r="32">
@@ -1421,7 +1421,7 @@
         <v>有时会害羞，比较内向</v>
       </c>
       <c r="J32" t="str">
-        <v>我是一个……的人 31. 有时会害羞，比较内向</v>
+        <v>我是一个有时会害羞，比较内向的人</v>
       </c>
     </row>
     <row r="33">
@@ -1453,7 +1453,7 @@
         <v>乐于助人，待人无私</v>
       </c>
       <c r="J33" t="str">
-        <v>我是一个……的人 32. 乐于助人，待人无私</v>
+        <v>我是一个乐于助人，待人无私的人</v>
       </c>
     </row>
     <row r="34">
@@ -1485,7 +1485,7 @@
         <v>习惯让事物保持整洁有序</v>
       </c>
       <c r="J34" t="str">
-        <v>我是一个……的人 33. 习惯让事物保持整洁有序</v>
+        <v>我是一个习惯让事物保持整洁有序的人</v>
       </c>
     </row>
     <row r="35">
@@ -1517,7 +1517,7 @@
         <v>时常忧心忡忡，担心很多事情</v>
       </c>
       <c r="J35" t="str">
-        <v>我是一个……的人 34. 时常忧心忡忡，担心很多事情</v>
+        <v>我是一个时常忧心忡忡，担心很多事情的人</v>
       </c>
     </row>
     <row r="36">
@@ -1549,7 +1549,7 @@
         <v>重视艺术与审美</v>
       </c>
       <c r="J36" t="str">
-        <v>我是一个……的人 35. 重视艺术与审美</v>
+        <v>我是一个重视艺术与审美的人</v>
       </c>
     </row>
     <row r="37">
@@ -1581,7 +1581,7 @@
         <v>感觉自己很难对他人产生影响</v>
       </c>
       <c r="J37" t="str">
-        <v>我是一个……的人 36. 感觉自己很难对他人产生影响</v>
+        <v>我是一个感觉自己很难对他人产生影响的人</v>
       </c>
     </row>
     <row r="38">
@@ -1613,7 +1613,7 @@
         <v>有时对人比较粗鲁</v>
       </c>
       <c r="J38" t="str">
-        <v>我是一个……的人 37. 有时对人比较粗鲁</v>
+        <v>我是一个有时对人比较粗鲁的人</v>
       </c>
     </row>
     <row r="39">
@@ -1645,7 +1645,7 @@
         <v>有效率，做事有始有终</v>
       </c>
       <c r="J39" t="str">
-        <v>我是一个……的人 38. 有效率，做事有始有终</v>
+        <v>我是一个有效率，做事有始有终的人</v>
       </c>
     </row>
     <row r="40">
@@ -1677,7 +1677,7 @@
         <v>时常觉得悲伤</v>
       </c>
       <c r="J40" t="str">
-        <v>我是一个……的人 39. 时常觉得悲伤</v>
+        <v>我是一个时常觉得悲伤的人</v>
       </c>
     </row>
     <row r="41">
@@ -1709,7 +1709,7 @@
         <v>思想深刻</v>
       </c>
       <c r="J41" t="str">
-        <v>我是一个……的人 40. 思想深刻</v>
+        <v>我是一个思想深刻的人</v>
       </c>
     </row>
     <row r="42">
@@ -1741,7 +1741,7 @@
         <v>精力充沛</v>
       </c>
       <c r="J42" t="str">
-        <v>我是一个……的人 41. 精力充沛</v>
+        <v>我是一个精力充沛的人</v>
       </c>
     </row>
     <row r="43">
@@ -1773,7 +1773,7 @@
         <v>不相信别人，怀疑别人的意图</v>
       </c>
       <c r="J43" t="str">
-        <v>我是一个……的人 42. 不相信别人，怀疑别人的意图</v>
+        <v>我是一个不相信别人，怀疑别人的意图的人</v>
       </c>
     </row>
     <row r="44">
@@ -1805,7 +1805,7 @@
         <v>可靠的，总是值得他人信赖</v>
       </c>
       <c r="J44" t="str">
-        <v>我是一个……的人 43. 可靠的，总是值得他人信赖</v>
+        <v>我是一个可靠的，总是值得他人信赖的人</v>
       </c>
     </row>
     <row r="45">
@@ -1837,7 +1837,7 @@
         <v>能够控制自己的情绪</v>
       </c>
       <c r="J45" t="str">
-        <v>我是一个……的人 44. 能够控制自己的情绪</v>
+        <v>我是一个能够控制自己的情绪的人</v>
       </c>
     </row>
     <row r="46">
@@ -1869,7 +1869,7 @@
         <v>缺乏想象力</v>
       </c>
       <c r="J46" t="str">
-        <v>我是一个……的人 45. 缺乏想象力</v>
+        <v>我是一个缺乏想象力的人</v>
       </c>
     </row>
     <row r="47">
@@ -1901,7 +1901,7 @@
         <v>爱说话，健谈</v>
       </c>
       <c r="J47" t="str">
-        <v>我是一个……的人 46. 爱说话，健谈</v>
+        <v>我是一个爱说话，健谈的人</v>
       </c>
     </row>
     <row r="48">
@@ -1933,7 +1933,7 @@
         <v>有时对人冷淡，漠不关心</v>
       </c>
       <c r="J48" t="str">
-        <v>我是一个……的人 47. 有时对人冷淡，漠不关心</v>
+        <v>我是一个有时对人冷淡，漠不关心的人</v>
       </c>
     </row>
     <row r="49">
@@ -1965,7 +1965,7 @@
         <v>乱糟糟的，不爱收拾</v>
       </c>
       <c r="J49" t="str">
-        <v>我是一个……的人 48. 乱糟糟的，不爱收拾</v>
+        <v>我是一个乱糟糟的，不爱收拾的人</v>
       </c>
     </row>
     <row r="50">
@@ -1997,7 +1997,7 @@
         <v>很少觉得焦虑或者害怕</v>
       </c>
       <c r="J50" t="str">
-        <v>我是一个……的人 49. 很少觉得焦虑或者害怕</v>
+        <v>我是一个很少觉得焦虑或者害怕的人</v>
       </c>
     </row>
     <row r="51">
@@ -2029,7 +2029,7 @@
         <v>觉得诗歌、戏剧很无聊</v>
       </c>
       <c r="J51" t="str">
-        <v>我是一个……的人 50. 觉得诗歌、戏剧很无聊</v>
+        <v>我是一个觉得诗歌、戏剧很无聊的人</v>
       </c>
     </row>
     <row r="52">
@@ -2061,7 +2061,7 @@
         <v>更喜欢让别人来领头负责</v>
       </c>
       <c r="J52" t="str">
-        <v>我是一个……的人 51. 更喜欢让别人来领头负责</v>
+        <v>我是一个更喜欢让别人来领头负责的人</v>
       </c>
     </row>
     <row r="53">
@@ -2093,7 +2093,7 @@
         <v>待人谦逊礼让</v>
       </c>
       <c r="J53" t="str">
-        <v>我是一个……的人 52. 待人谦逊礼让</v>
+        <v>我是一个待人谦逊礼让的人</v>
       </c>
     </row>
     <row r="54">
@@ -2125,7 +2125,7 @@
         <v>有恒心，能坚持把事情做完</v>
       </c>
       <c r="J54" t="str">
-        <v>我是一个……的人 53. 有恒心，能坚持把事情做完</v>
+        <v>我是一个有恒心，能坚持把事情做完的人</v>
       </c>
     </row>
     <row r="55">
@@ -2157,7 +2157,7 @@
         <v>时常觉得郁郁寡欢</v>
       </c>
       <c r="J55" t="str">
-        <v>我是一个……的人 54. 时常觉得郁郁寡欢</v>
+        <v>我是一个时常觉得郁郁寡欢的人</v>
       </c>
     </row>
     <row r="56">
@@ -2189,7 +2189,7 @@
         <v>对抽象的概念和想法没什么兴趣</v>
       </c>
       <c r="J56" t="str">
-        <v>我是一个……的人 55. 对抽象的概念和想法没什么兴趣</v>
+        <v>我是一个对抽象的概念和想法没什么兴趣的人</v>
       </c>
     </row>
     <row r="57">
@@ -2221,7 +2221,7 @@
         <v>充满热情</v>
       </c>
       <c r="J57" t="str">
-        <v>我是一个……的人 56. 充满热情</v>
+        <v>我是一个充满热情的人</v>
       </c>
     </row>
     <row r="58">
@@ -2253,7 +2253,7 @@
         <v>把人往最好的方面想</v>
       </c>
       <c r="J58" t="str">
-        <v>我是一个……的人 57. 把人往最好的方面想</v>
+        <v>我是一个把人往最好的方面想的人</v>
       </c>
     </row>
     <row r="59">
@@ -2285,7 +2285,7 @@
         <v>有时候会做出一些不负责任的行为</v>
       </c>
       <c r="J59" t="str">
-        <v>我是一个……的人 58. 有时候会做出一些不负责任的行为</v>
+        <v>我是一个有时候会做出一些不负责任的行为的人</v>
       </c>
     </row>
     <row r="60">
@@ -2317,7 +2317,7 @@
         <v>情绪多变，容易愤怒</v>
       </c>
       <c r="J60" t="str">
-        <v>我是一个……的人 59. 情绪多变，容易愤怒</v>
+        <v>我是一个情绪多变，容易愤怒的人</v>
       </c>
     </row>
     <row r="61">
@@ -2349,7 +2349,7 @@
         <v>有创意，能想出新点子</v>
       </c>
       <c r="J61" t="str">
-        <v>我是一个……的人 60. 有创意，能想出新点子</v>
+        <v>我是一个有创意，能想出新点子的人</v>
       </c>
     </row>
   </sheetData>
